--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575126619</v>
+        <v>46157.93119279808</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119279808</v>
+        <v>46157.93184974155</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93184974155</v>
+        <v>46157.93406515518</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406515518</v>
+        <v>46157.93724556063</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724556063</v>
+        <v>46158.28222243532</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222243532</v>
+        <v>46158.29704736838</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29704736838</v>
+        <v>46158.29822135725</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822135725</v>
+        <v>46158.3339319464</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3339319464</v>
+        <v>46158.36862981876</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862981876</v>
+        <v>46158.37293950863</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
